--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -71069,6 +71069,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>14112</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>1.18799996376038</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="G2720" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="H2720" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -71095,6 +71095,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>50786</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>1.13499999046326</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G2721" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="H2721" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -71121,6 +71121,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>82580</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>1.44900000095367</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.34800004959106</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="G2722" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="H2722" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -71147,6 +71147,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>167644</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>1.64499998092651</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>1.46800005435944</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>1.56099998950958</v>
+      </c>
+      <c r="G2723" t="n">
+        <v>1.56099998950958</v>
+      </c>
+      <c r="H2723" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -71225,6 +71225,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>10662</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>1.49899995326996</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>1.49979996681213</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>1.49979996681213</v>
+      </c>
+      <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -71251,6 +71251,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>23534</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>1.41199994087219</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>1.45019996166229</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>1.41199994087219</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>1.41199994087219</v>
+      </c>
+      <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -71277,6 +71277,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>1836</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>1.46899998188019</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>1.46899998188019</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -71303,6 +71303,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>33782</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>1.53900003433228</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>1.40100002288818</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>1.40100002288818</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>1.53900003433228</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>1.53900003433228</v>
+      </c>
+      <c r="H2729" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -71381,6 +71381,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>40759</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="H2732" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>1.40299999713898</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>1.4099999666214</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>4836</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>1.40299999713898</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>1.42499995231628</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>1.42499995231628</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>1.4099999666214</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>6509</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>1.41499996185303</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>1.41499996185303</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>1.41499996185303</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>11852</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>1.41100001335144</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>1.41100001335144</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1.45000004768372</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>33312</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>1.44959998130798</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>1.40199995040894</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>53512</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1.37020003795624</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -71646,7 +71646,7 @@
         <v>46309.2916666667</v>
       </c>
       <c r="B2742" t="n">
-        <v>23071</v>
+        <v>23072</v>
       </c>
       <c r="C2742" t="n">
         <v>1.31500005722046</v>
@@ -71664,6 +71664,32 @@
         <v>1.23000001907349</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>6789</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>1.27900004386902</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>1.27900004386902</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -71693,6 +71693,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>23469</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>1.21619999408722</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>1.26979994773865</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>1.25979995727539</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>1.25979995727539</v>
+      </c>
+      <c r="H2744" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -79983,6 +79983,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>1.21220004558563</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>1.17019999027252</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>14115</v>
+      </c>
+      <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -80012,6 +80012,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>1.26499998569489</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>19688</v>
+      </c>
+      <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -80041,6 +80041,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>1.23500001430511</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>1.23500001430511</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>1.19500005245209</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>1.19500005245209</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>1991</v>
+      </c>
+      <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -80070,6 +80070,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>1.23500001430511</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>2283</v>
+      </c>
+      <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -80099,6 +80099,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>3380</v>
+      </c>
+      <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -80128,6 +80128,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>2780</v>
+      </c>
+      <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -80157,6 +80157,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>1.27499997615814</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>1.27499997615814</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>3096</v>
+      </c>
+      <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -80186,6 +80186,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>9676</v>
+      </c>
+      <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPH.MI.xlsx
+++ b/data/EPH.MI.xlsx
@@ -80215,6 +80215,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>1.23500001430511</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>4445</v>
+      </c>
+      <c r="I2754" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
